--- a/____Unpublished__ProjectKaskan/unique_refs_comments.xlsx
+++ b/____Unpublished__ProjectKaskan/unique_refs_comments.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alleninstitute.sharepoint.com/sites/MammalianM1/Shared Documents/General/Species/Evo-M1-Trait-Data/____Unpublished__ProjectKaskan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="11_6ACA08970F2D1798E7481335482B57FF2B503C9F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50A09E69-9313-4F45-BFC5-BC2EF4D0B9E4}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="11_6ACA08970F2D1798E7481335482B57FF2B503C9F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B32F2D62-009B-E340-80F0-415370206339}"/>
   <bookViews>
-    <workbookView xWindow="300" yWindow="760" windowWidth="32820" windowHeight="20100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="35180" yWindow="-6780" windowWidth="34300" windowHeight="20180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="51">
   <si>
     <t>Source</t>
   </si>
@@ -145,9 +145,6 @@
     <t>Data Quality</t>
   </si>
   <si>
-    <t>Nannospalax_galili only. Cortical organization schematic, with scale, said to be adapted from Bronchti 2002. In fact Bronchto 2002 refer to Necxker 1992 as source of 3D alignment, and Necker 2002 seems to be source of the outline of the cortex</t>
-  </si>
-  <si>
     <t>Species</t>
   </si>
   <si>
@@ -161,6 +158,21 @@
   </si>
   <si>
     <t>organization schematic, seems similar to flat map</t>
+  </si>
+  <si>
+    <t>Nannospalax_galili only. Cortical organization schematic, with scale, said to be adapted from Bronchti 2002. In fact Bronchti 2002 refers to Necker 1992 as source of 3D alignment, and Necker 2002 seems to be source of the outline of the cortex</t>
+  </si>
+  <si>
+    <t>Correct ref</t>
+  </si>
+  <si>
+    <t>Correct figure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Krubitzer, L. A., &amp; Prescott, T. J. (2018). The combinatorial creature: Cortical phenotypes within and across lifetimes. Trends Neurosci, 41(10), 744-762. https://doi.org/10.1016/j.tins.2018.08.002 	</t>
+  </si>
+  <si>
+    <t>Figure 4.</t>
   </si>
 </sst>
 </file>
@@ -494,15 +506,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="167.5" customWidth="1"/>
+    <col min="1" max="1" width="167" customWidth="1"/>
     <col min="2" max="2" width="17.1640625" customWidth="1"/>
     <col min="3" max="3" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -519,95 +531,107 @@
         <v>40</v>
       </c>
       <c r="F1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+        <v>41</v>
+      </c>
+      <c r="G1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C2" t="s">
         <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
         <v>39</v>
       </c>
       <c r="F2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+      <c r="G2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -645,13 +669,13 @@
         <v>37</v>
       </c>
       <c r="D22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E22" t="s">
         <v>39</v>
       </c>
       <c r="F22" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
@@ -726,15 +750,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d42a73f51a03135be35f4acb272f8cf1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2ea21b36c10eaa86a5cb337ec7f4e0a6" ns2:_="" ns3:_="">
     <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
@@ -989,15 +1004,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E63810B5-A7DE-4276-9805-3FBF99E1CA75}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{896389EE-9F26-485E-9645-051A95C9855C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1014,4 +1030,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E63810B5-A7DE-4276-9805-3FBF99E1CA75}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>